--- a/exports/trend_1d/M&M_full_report.xlsx
+++ b/exports/trend_1d/M&M_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:U81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>7</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42034</v>
+        <v>42037</v>
       </c>
       <c r="H2" t="n">
-        <v>632.55</v>
+        <v>620.6</v>
       </c>
       <c r="I2" t="n">
         <v>631.5661222782001</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.02</v>
+        <v>-2.89</v>
       </c>
       <c r="L2" t="n">
-        <v>1.93</v>
+        <v>3.48</v>
       </c>
       <c r="M2" t="n">
         <v>0.16</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>9.960000000000001</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42053</v>
+        <v>42054</v>
       </c>
       <c r="H3" t="n">
-        <v>614.1</v>
+        <v>624.95</v>
       </c>
       <c r="I3" t="n">
         <v>615.6081360028854</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K3" t="n">
-        <v>1.05</v>
+        <v>-0.7</v>
       </c>
       <c r="L3" t="n">
         <v>3.53</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>10.43</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42082</v>
+        <v>42083</v>
       </c>
       <c r="H4" t="n">
-        <v>603.7</v>
+        <v>582.65</v>
       </c>
       <c r="I4" t="n">
         <v>588.2901149916852</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.4</v>
+        <v>-6.77</v>
       </c>
       <c r="L4" t="n">
-        <v>3.91</v>
+        <v>7.64</v>
       </c>
       <c r="M4" t="n">
         <v>1.58</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>10.45</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42139</v>
+        <v>42142</v>
       </c>
       <c r="H5" t="n">
-        <v>624.53</v>
+        <v>631.83</v>
       </c>
       <c r="I5" t="n">
         <v>631.3043219737373</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K5" t="n">
-        <v>-7.19</v>
+        <v>-8.44</v>
       </c>
       <c r="L5" t="n">
         <v>10.7</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.56</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42227</v>
+        <v>42228</v>
       </c>
       <c r="H6" t="n">
-        <v>669.78</v>
+        <v>649.7</v>
       </c>
       <c r="I6" t="n">
         <v>651.4581941538236</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K6" t="n">
-        <v>6.01</v>
+        <v>2.83</v>
       </c>
       <c r="L6" t="n">
         <v>7.44</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>10.12</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42275</v>
+        <v>42276</v>
       </c>
       <c r="H7" t="n">
-        <v>610.8</v>
+        <v>624.85</v>
       </c>
       <c r="I7" t="n">
         <v>620.6834935607528</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K7" t="n">
-        <v>5.99</v>
+        <v>3.82</v>
       </c>
       <c r="L7" t="n">
         <v>6.56</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>10.39</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42306</v>
+        <v>42307</v>
       </c>
       <c r="H8" t="n">
-        <v>613.9</v>
+        <v>591.8</v>
       </c>
       <c r="I8" t="n">
         <v>599.3295304031852</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.75</v>
+        <v>-5.29</v>
       </c>
       <c r="L8" t="n">
-        <v>3.85</v>
+        <v>6.11</v>
       </c>
       <c r="M8" t="n">
         <v>1.28</v>
       </c>
       <c r="N8" t="n">
-        <v>2.39</v>
+        <v>3.6</v>
       </c>
       <c r="O8" t="n">
         <v>2.3</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>9.58</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42327</v>
+        <v>42328</v>
       </c>
       <c r="H9" t="n">
-        <v>646.05</v>
+        <v>657.63</v>
       </c>
       <c r="I9" t="n">
         <v>648.4717790172807</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K9" t="n">
-        <v>-9.17</v>
+        <v>-11.12</v>
       </c>
       <c r="L9" t="n">
-        <v>10.17</v>
+        <v>11.95</v>
       </c>
       <c r="M9" t="n">
         <v>1.39</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>7.92</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42348</v>
+        <v>42349</v>
       </c>
       <c r="H10" t="n">
-        <v>645.35</v>
+        <v>630.95</v>
       </c>
       <c r="I10" t="n">
         <v>644.3972475641195</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.87</v>
+        <v>-4.06</v>
       </c>
       <c r="L10" t="n">
-        <v>2.38</v>
+        <v>5.42</v>
       </c>
       <c r="M10" t="n">
         <v>0.75</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>7.91</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42429</v>
+        <v>42430</v>
       </c>
       <c r="H11" t="n">
-        <v>614.05</v>
+        <v>634.05</v>
       </c>
       <c r="I11" t="n">
         <v>618.9891958643656</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K11" t="n">
-        <v>2.68</v>
+        <v>-0.49</v>
       </c>
       <c r="L11" t="n">
         <v>3.37</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>11.76</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42625</v>
+        <v>42627</v>
       </c>
       <c r="H12" t="n">
-        <v>712.98</v>
+        <v>705.78</v>
       </c>
       <c r="I12" t="n">
         <v>708.2481310003006</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K12" t="n">
-        <v>12.45</v>
+        <v>11.31</v>
       </c>
       <c r="L12" t="n">
         <v>6.63</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>131</v>
+        <v>132</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>6.66</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42759</v>
+        <v>42760</v>
       </c>
       <c r="H13" t="n">
-        <v>610.35</v>
+        <v>621.9</v>
       </c>
       <c r="I13" t="n">
         <v>620.4137002684425</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K13" t="n">
-        <v>13.52</v>
+        <v>11.88</v>
       </c>
       <c r="L13" t="n">
         <v>3.06</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>7.12</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42977</v>
+        <v>42978</v>
       </c>
       <c r="H14" t="n">
-        <v>679.08</v>
+        <v>672.4</v>
       </c>
       <c r="I14" t="n">
         <v>672.8328316592236</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K14" t="n">
-        <v>9.19</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="L14" t="n">
         <v>2.56</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>147</v>
+        <v>148</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>7</v>
+      </c>
+      <c r="U14" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>5.23</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43018</v>
+        <v>43019</v>
       </c>
       <c r="H15" t="n">
-        <v>652.55</v>
+        <v>659.73</v>
       </c>
       <c r="I15" t="n">
         <v>655.7303197048202</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K15" t="n">
-        <v>2.95</v>
+        <v>1.88</v>
       </c>
       <c r="L15" t="n">
         <v>1.15</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>5.76</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43074</v>
+        <v>43075</v>
       </c>
       <c r="H16" t="n">
-        <v>694.1</v>
+        <v>683.73</v>
       </c>
       <c r="I16" t="n">
         <v>684.3598560757662</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K16" t="n">
-        <v>5.21</v>
+        <v>3.64</v>
       </c>
       <c r="L16" t="n">
         <v>1.02</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>6.14</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43083</v>
+        <v>43084</v>
       </c>
       <c r="H17" t="n">
-        <v>715.8</v>
+        <v>741.7</v>
       </c>
       <c r="I17" t="n">
         <v>722.9897641422388</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.69</v>
+        <v>-8.48</v>
       </c>
       <c r="L17" t="n">
-        <v>5.01</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>0.68</v>
+        <v>0.76</v>
       </c>
       <c r="N17" t="n">
-        <v>2.17</v>
+        <v>3.62</v>
       </c>
       <c r="O17" t="n">
         <v>-1.49</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>6.66</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43147</v>
+        <v>43150</v>
       </c>
       <c r="H18" t="n">
-        <v>743.75</v>
+        <v>724.65</v>
       </c>
       <c r="I18" t="n">
         <v>730.9415252346872</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K18" t="n">
-        <v>0.28</v>
+        <v>-2.3</v>
       </c>
       <c r="L18" t="n">
-        <v>2.86</v>
+        <v>3.46</v>
       </c>
       <c r="M18" t="n">
         <v>2.2</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>8.609999999999999</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43192</v>
+        <v>43193</v>
       </c>
       <c r="H19" t="n">
-        <v>748.05</v>
+        <v>770.1</v>
       </c>
       <c r="I19" t="n">
         <v>767.0386880537957</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.23</v>
+        <v>-6.27</v>
       </c>
       <c r="L19" t="n">
-        <v>3.77</v>
+        <v>6.45</v>
       </c>
       <c r="M19" t="n">
         <v>1.35</v>
       </c>
       <c r="N19" t="n">
-        <v>2.66</v>
+        <v>2.95</v>
       </c>
       <c r="O19" t="n">
         <v>-2.57</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>7.9</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43346</v>
+        <v>43347</v>
       </c>
       <c r="H20" t="n">
-        <v>947.8</v>
+        <v>931.75</v>
       </c>
       <c r="I20" t="n">
         <v>933.9015489354077</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K20" t="n">
-        <v>23.07</v>
+        <v>20.99</v>
       </c>
       <c r="L20" t="n">
         <v>3.25</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>6</v>
+      </c>
+      <c r="U20" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>7.66</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43453</v>
+        <v>43454</v>
       </c>
       <c r="H21" t="n">
-        <v>782.65</v>
+        <v>795.45</v>
       </c>
       <c r="I21" t="n">
         <v>783.2835218695863</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K21" t="n">
-        <v>16</v>
+        <v>14.63</v>
       </c>
       <c r="L21" t="n">
         <v>4.93</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>9.109999999999999</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43466</v>
+        <v>43467</v>
       </c>
       <c r="H22" t="n">
-        <v>773.35</v>
+        <v>741.7</v>
       </c>
       <c r="I22" t="n">
         <v>747.4194638690175</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.78</v>
+        <v>-6.76</v>
       </c>
       <c r="L22" t="n">
-        <v>3.04</v>
+        <v>7.59</v>
       </c>
       <c r="M22" t="n">
         <v>0.38</v>
       </c>
       <c r="N22" t="n">
-        <v>3.79</v>
+        <v>4.09</v>
       </c>
       <c r="O22" t="n">
         <v>1.64</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>10.81</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43532</v>
+        <v>43535</v>
       </c>
       <c r="H23" t="n">
-        <v>670.15</v>
+        <v>681.05</v>
       </c>
       <c r="I23" t="n">
         <v>676.1600886213802</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K23" t="n">
-        <v>9.65</v>
+        <v>8.18</v>
       </c>
       <c r="L23" t="n">
         <v>4.19</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>7.37</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43581</v>
+        <v>43585</v>
       </c>
       <c r="H24" t="n">
-        <v>659.45</v>
+        <v>645.3</v>
       </c>
       <c r="I24" t="n">
         <v>650.6149975861005</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.17</v>
+        <v>-5.25</v>
       </c>
       <c r="L24" t="n">
-        <v>4.38</v>
+        <v>6.03</v>
       </c>
       <c r="M24" t="n">
         <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="O24" t="n">
         <v>1.63</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>7.18</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43602</v>
+        <v>43605</v>
       </c>
       <c r="H25" t="n">
-        <v>619.65</v>
+        <v>653.25</v>
       </c>
       <c r="I25" t="n">
         <v>647.4334067067493</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K25" t="n">
-        <v>3.97</v>
+        <v>-1.23</v>
       </c>
       <c r="L25" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="M25" t="n">
-        <v>0.61</v>
+        <v>2.48</v>
       </c>
       <c r="N25" t="n">
-        <v>2.38</v>
+        <v>5.42</v>
       </c>
       <c r="O25" t="n">
         <v>-2.15</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>8.85</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43634</v>
+        <v>43635</v>
       </c>
       <c r="H26" t="n">
-        <v>625.9</v>
+        <v>615.15</v>
       </c>
       <c r="I26" t="n">
         <v>618.7342661509003</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.19</v>
+        <v>-5.83</v>
       </c>
       <c r="L26" t="n">
-        <v>5.07</v>
+        <v>6.93</v>
       </c>
       <c r="M26" t="n">
         <v>1.81</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>8.68</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43648</v>
+        <v>43649</v>
       </c>
       <c r="H27" t="n">
-        <v>666.25</v>
+        <v>669.25</v>
       </c>
       <c r="I27" t="n">
         <v>668.5625206109552</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K27" t="n">
-        <v>-8.31</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>8.67</v>
+        <v>9.73</v>
       </c>
       <c r="M27" t="n">
         <v>0.63</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>5.97</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43655</v>
+        <v>43656</v>
       </c>
       <c r="H28" t="n">
-        <v>632.7</v>
+        <v>621.65</v>
       </c>
       <c r="I28" t="n">
         <v>631.1987523607279</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K28" t="n">
-        <v>-5.46</v>
+        <v>-7.11</v>
       </c>
       <c r="L28" t="n">
-        <v>6.43</v>
+        <v>7.49</v>
       </c>
       <c r="M28" t="n">
         <v>0.61</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>8.25</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H29" t="n">
-        <v>519.3</v>
+        <v>568.9</v>
       </c>
       <c r="I29" t="n">
         <v>567.5419679803288</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K29" t="n">
-        <v>16.46</v>
+        <v>8.49</v>
       </c>
       <c r="L29" t="n">
         <v>2.63</v>
@@ -2094,7 +2441,7 @@
         <v>3.65</v>
       </c>
       <c r="N29" t="n">
-        <v>4.19</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="O29" t="n">
         <v>-1.75</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>14.61</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43789</v>
+        <v>43790</v>
       </c>
       <c r="H30" t="n">
-        <v>560.45</v>
+        <v>551.8</v>
       </c>
       <c r="I30" t="n">
         <v>557.7403984018955</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.49</v>
+        <v>-3.01</v>
       </c>
       <c r="L30" t="n">
         <v>8.83</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>8.75</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43839</v>
+        <v>43840</v>
       </c>
       <c r="H31" t="n">
-        <v>541.25</v>
+        <v>546.6</v>
       </c>
       <c r="I31" t="n">
         <v>543.6106245941158</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K31" t="n">
-        <v>1.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L31" t="n">
         <v>1.97</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>6.34</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43868</v>
+        <v>43871</v>
       </c>
       <c r="H32" t="n">
-        <v>569.1</v>
+        <v>528.4</v>
       </c>
       <c r="I32" t="n">
         <v>541.1482852410926</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K32" t="n">
-        <v>4.12</v>
+        <v>-3.33</v>
       </c>
       <c r="L32" t="n">
-        <v>3.23</v>
+        <v>3.76</v>
       </c>
       <c r="M32" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>3.87</v>
+        <v>7.15</v>
       </c>
       <c r="O32" t="n">
         <v>0.99</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>14.99</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43929</v>
+        <v>43930</v>
       </c>
       <c r="H33" t="n">
-        <v>326.4</v>
+        <v>381.4</v>
       </c>
       <c r="I33" t="n">
         <v>362.6823569702606</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K33" t="n">
-        <v>38.23</v>
+        <v>27.82</v>
       </c>
       <c r="L33" t="n">
         <v>7.31</v>
@@ -2322,7 +2717,7 @@
         <v>5.27</v>
       </c>
       <c r="N33" t="n">
-        <v>14.36</v>
+        <v>16.85</v>
       </c>
       <c r="O33" t="n">
         <v>-7.15</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>31.9</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44097</v>
+        <v>44098</v>
       </c>
       <c r="H34" t="n">
-        <v>612.6</v>
+        <v>575.1</v>
       </c>
       <c r="I34" t="n">
         <v>584.7313587123617</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K34" t="n">
-        <v>60.62</v>
+        <v>50.79</v>
       </c>
       <c r="L34" t="n">
         <v>15.94</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>116</v>
+        <v>117</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>6</v>
+      </c>
+      <c r="U34" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>15.3</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44152</v>
+        <v>44153</v>
       </c>
       <c r="H35" t="n">
-        <v>637.25</v>
+        <v>705.75</v>
       </c>
       <c r="I35" t="n">
         <v>647.1412555795804</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K35" t="n">
-        <v>-10.81</v>
+        <v>-22.72</v>
       </c>
       <c r="L35" t="n">
-        <v>13.79</v>
+        <v>23.45</v>
       </c>
       <c r="M35" t="n">
         <v>1.53</v>
       </c>
       <c r="N35" t="n">
-        <v>3.87</v>
+        <v>10.75</v>
       </c>
       <c r="O35" t="n">
         <v>-6.12</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>13.59</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44183</v>
+        <v>44186</v>
       </c>
       <c r="H36" t="n">
-        <v>733.6</v>
+        <v>685.95</v>
       </c>
       <c r="I36" t="n">
         <v>693.7474507684493</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K36" t="n">
-        <v>3.95</v>
+        <v>-2.81</v>
       </c>
       <c r="L36" t="n">
         <v>9.74</v>
@@ -2493,7 +2924,7 @@
         <v>1.32</v>
       </c>
       <c r="N36" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="O36" t="n">
         <v>10.75</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>12.79</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44203</v>
+        <v>44204</v>
       </c>
       <c r="H37" t="n">
-        <v>744.4</v>
+        <v>770.5</v>
       </c>
       <c r="I37" t="n">
         <v>763.6196148918091</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K37" t="n">
-        <v>-8.52</v>
+        <v>-12.33</v>
       </c>
       <c r="L37" t="n">
-        <v>10.07</v>
+        <v>12.66</v>
       </c>
       <c r="M37" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="N37" t="n">
-        <v>2.37</v>
+        <v>3.51</v>
       </c>
       <c r="O37" t="n">
         <v>-6.5</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>10.07</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44224</v>
+        <v>44225</v>
       </c>
       <c r="H38" t="n">
-        <v>765</v>
+        <v>749.6</v>
       </c>
       <c r="I38" t="n">
         <v>760.9227309153737</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.71</v>
+        <v>-2.71</v>
       </c>
       <c r="L38" t="n">
         <v>3.31</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>15.51</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44230</v>
+        <v>44231</v>
       </c>
       <c r="H39" t="n">
-        <v>833.2</v>
+        <v>866.5</v>
       </c>
       <c r="I39" t="n">
         <v>865.8780177715605</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K39" t="n">
-        <v>-11.15</v>
+        <v>-15.59</v>
       </c>
       <c r="L39" t="n">
-        <v>14.58</v>
+        <v>19.2</v>
       </c>
       <c r="M39" t="n">
         <v>1.87</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>13.57</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44252</v>
+        <v>44253</v>
       </c>
       <c r="H40" t="n">
-        <v>859</v>
+        <v>806.4</v>
       </c>
       <c r="I40" t="n">
         <v>814.2641896055843</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.87</v>
+        <v>-6.94</v>
       </c>
       <c r="L40" t="n">
-        <v>5.47</v>
+        <v>7.85</v>
       </c>
       <c r="M40" t="n">
-        <v>0.79</v>
+        <v>1.27</v>
       </c>
       <c r="N40" t="n">
-        <v>4.79</v>
+        <v>6.12</v>
       </c>
       <c r="O40" t="n">
         <v>4</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>15.63</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44336</v>
+        <v>44337</v>
       </c>
       <c r="H41" t="n">
-        <v>803.25</v>
+        <v>818.95</v>
       </c>
       <c r="I41" t="n">
         <v>814.265207425193</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K41" t="n">
-        <v>0.39</v>
+        <v>-1.56</v>
       </c>
       <c r="L41" t="n">
         <v>8.66</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>9.949999999999999</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44396</v>
+        <v>44397</v>
       </c>
       <c r="H42" t="n">
-        <v>775.8</v>
+        <v>760.2</v>
       </c>
       <c r="I42" t="n">
         <v>761.143498169498</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K42" t="n">
-        <v>-5.27</v>
+        <v>-7.17</v>
       </c>
       <c r="L42" t="n">
-        <v>6.91</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="M42" t="n">
         <v>2.58</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>5.91</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44417</v>
+        <v>44418</v>
       </c>
       <c r="H43" t="n">
-        <v>774.95</v>
+        <v>786.3</v>
       </c>
       <c r="I43" t="n">
         <v>775.8583968826255</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.94</v>
+        <v>-3.43</v>
       </c>
       <c r="L43" t="n">
-        <v>2.87</v>
+        <v>3.89</v>
       </c>
       <c r="M43" t="n">
         <v>0.93</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>6.56</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44456</v>
+        <v>44459</v>
       </c>
       <c r="H44" t="n">
-        <v>754.15</v>
+        <v>738.05</v>
       </c>
       <c r="I44" t="n">
         <v>739.6784151570075</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K44" t="n">
-        <v>-4.09</v>
+        <v>-6.14</v>
       </c>
       <c r="L44" t="n">
-        <v>5.84</v>
+        <v>6.88</v>
       </c>
       <c r="M44" t="n">
         <v>0.63</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>7.14</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44463</v>
+        <v>44466</v>
       </c>
       <c r="H45" t="n">
-        <v>779.45</v>
+        <v>811.35</v>
       </c>
       <c r="I45" t="n">
         <v>780.3601290830272</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K45" t="n">
-        <v>-5.61</v>
+        <v>-9.93</v>
       </c>
       <c r="L45" t="n">
-        <v>5.96</v>
+        <v>10.26</v>
       </c>
       <c r="M45" t="n">
-        <v>0.53</v>
+        <v>1.29</v>
       </c>
       <c r="N45" t="n">
-        <v>2.77</v>
+        <v>4.09</v>
       </c>
       <c r="O45" t="n">
         <v>-2.13</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>8.33</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="H46" t="n">
-        <v>891.2</v>
+        <v>853.75</v>
       </c>
       <c r="I46" t="n">
         <v>878.7967583146093</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K46" t="n">
-        <v>9.84</v>
+        <v>5.23</v>
       </c>
       <c r="L46" t="n">
         <v>3.49</v>
@@ -3063,7 +3614,7 @@
         <v>0.85</v>
       </c>
       <c r="N46" t="n">
-        <v>3.22</v>
+        <v>4.2</v>
       </c>
       <c r="O46" t="n">
         <v>4.09</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>11.12</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44572</v>
+        <v>44573</v>
       </c>
       <c r="H47" t="n">
-        <v>841.4</v>
+        <v>880.55</v>
       </c>
       <c r="I47" t="n">
         <v>879.6794431673115</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K47" t="n">
-        <v>1.45</v>
+        <v>-3.14</v>
       </c>
       <c r="L47" t="n">
         <v>3.66</v>
@@ -3120,7 +3683,7 @@
         <v>1.98</v>
       </c>
       <c r="N47" t="n">
-        <v>2.46</v>
+        <v>4.65</v>
       </c>
       <c r="O47" t="n">
         <v>-4.2</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>9.07</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44596</v>
+        <v>44599</v>
       </c>
       <c r="H48" t="n">
-        <v>841.7</v>
+        <v>829.5</v>
       </c>
       <c r="I48" t="n">
         <v>832.367025114379</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.41</v>
+        <v>-5.8</v>
       </c>
       <c r="L48" t="n">
-        <v>5.04</v>
+        <v>6.63</v>
       </c>
       <c r="M48" t="n">
         <v>1.04</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>9.130000000000001</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44636</v>
+        <v>44637</v>
       </c>
       <c r="H49" t="n">
-        <v>773.65</v>
+        <v>794.4</v>
       </c>
       <c r="I49" t="n">
         <v>785.0946060438225</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K49" t="n">
-        <v>6.73</v>
+        <v>4.23</v>
       </c>
       <c r="L49" t="n">
         <v>5.91</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>11.25</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44881</v>
+        <v>44882</v>
       </c>
       <c r="H50" t="n">
-        <v>1286.7</v>
+        <v>1259.35</v>
       </c>
       <c r="I50" t="n">
         <v>1268.836139730624</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K50" t="n">
-        <v>61.97</v>
+        <v>58.53</v>
       </c>
       <c r="L50" t="n">
         <v>5.43</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>165</v>
+        <v>166</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>9</v>
+      </c>
+      <c r="U50" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>7.94</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44932</v>
+        <v>44935</v>
       </c>
       <c r="H51" t="n">
-        <v>1264.9</v>
+        <v>1310.35</v>
       </c>
       <c r="I51" t="n">
         <v>1304.431710306307</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.44</v>
+        <v>-4.05</v>
       </c>
       <c r="L51" t="n">
         <v>4.57</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>7.91</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44980</v>
+        <v>44981</v>
       </c>
       <c r="H52" t="n">
-        <v>1313.95</v>
+        <v>1280.2</v>
       </c>
       <c r="I52" t="n">
         <v>1280.631698881642</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K52" t="n">
-        <v>0.27</v>
+        <v>-2.3</v>
       </c>
       <c r="L52" t="n">
         <v>2.95</v>
@@ -3405,7 +4028,7 @@
         <v>0.6</v>
       </c>
       <c r="N52" t="n">
-        <v>2.37</v>
+        <v>2.57</v>
       </c>
       <c r="O52" t="n">
         <v>3.59</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>9.130000000000001</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45042</v>
+        <v>45043</v>
       </c>
       <c r="H53" t="n">
-        <v>1213.55</v>
+        <v>1224</v>
       </c>
       <c r="I53" t="n">
         <v>1222.039530393068</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K53" t="n">
-        <v>5.21</v>
+        <v>4.39</v>
       </c>
       <c r="L53" t="n">
         <v>3.15</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>4.98</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45133</v>
+        <v>45134</v>
       </c>
       <c r="H54" t="n">
-        <v>1544.85</v>
+        <v>1447.4</v>
       </c>
       <c r="I54" t="n">
         <v>1471.27987323975</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K54" t="n">
-        <v>26.21</v>
+        <v>18.25</v>
       </c>
       <c r="L54" t="n">
         <v>1.3</v>
       </c>
       <c r="M54" t="n">
-        <v>0.67</v>
+        <v>2.97</v>
       </c>
       <c r="N54" t="n">
-        <v>1.8</v>
+        <v>6.31</v>
       </c>
       <c r="O54" t="n">
         <v>0.86</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>9.69</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45167</v>
+        <v>45168</v>
       </c>
       <c r="H55" t="n">
-        <v>1560.85</v>
+        <v>1583.2</v>
       </c>
       <c r="I55" t="n">
         <v>1574.211875854037</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K55" t="n">
-        <v>-7.84</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>9.34</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="M55" t="n">
         <v>1.66</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>6.56</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45202</v>
+        <v>45203</v>
       </c>
       <c r="H56" t="n">
-        <v>1537.4</v>
+        <v>1522.1</v>
       </c>
       <c r="I56" t="n">
         <v>1526.782037282898</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K56" t="n">
-        <v>-2.89</v>
+        <v>-3.86</v>
       </c>
       <c r="L56" t="n">
-        <v>4.43</v>
+        <v>5.14</v>
       </c>
       <c r="M56" t="n">
         <v>1.3</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>7.91</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45245</v>
+        <v>45246</v>
       </c>
       <c r="H57" t="n">
-        <v>1544.15</v>
+        <v>1569.5</v>
       </c>
       <c r="I57" t="n">
         <v>1566.524530763073</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.45</v>
+        <v>-3.11</v>
       </c>
       <c r="L57" t="n">
         <v>4.06</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>6.67</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45296</v>
+        <v>45299</v>
       </c>
       <c r="H58" t="n">
-        <v>1642</v>
+        <v>1616.15</v>
       </c>
       <c r="I58" t="n">
         <v>1617.551255767881</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K58" t="n">
-        <v>4.62</v>
+        <v>2.97</v>
       </c>
       <c r="L58" t="n">
         <v>2.2</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>8.02</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45324</v>
+        <v>45327</v>
       </c>
       <c r="H59" t="n">
-        <v>1660.75</v>
+        <v>1703.55</v>
       </c>
       <c r="I59" t="n">
         <v>1699.54044233632</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.76</v>
+        <v>-5.41</v>
       </c>
       <c r="L59" t="n">
-        <v>5.35</v>
+        <v>5.98</v>
       </c>
       <c r="M59" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="N59" t="n">
-        <v>2.37</v>
+        <v>2.58</v>
       </c>
       <c r="O59" t="n">
         <v>-1.57</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>8.32</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="H60" t="n">
-        <v>1890.55</v>
+        <v>1799.5</v>
       </c>
       <c r="I60" t="n">
         <v>1821.907165464149</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K60" t="n">
-        <v>10.98</v>
+        <v>5.63</v>
       </c>
       <c r="L60" t="n">
         <v>4.7</v>
@@ -3861,7 +4580,7 @@
         <v>2.06</v>
       </c>
       <c r="N60" t="n">
-        <v>3.71</v>
+        <v>4.82</v>
       </c>
       <c r="O60" t="n">
         <v>2.58</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>11.21</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45385</v>
+        <v>45386</v>
       </c>
       <c r="H61" t="n">
-        <v>1989.3</v>
+        <v>2002.7</v>
       </c>
       <c r="I61" t="n">
         <v>1999.009548655133</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K61" t="n">
-        <v>-10.55</v>
+        <v>-11.29</v>
       </c>
       <c r="L61" t="n">
-        <v>11.33</v>
+        <v>11.98</v>
       </c>
       <c r="M61" t="n">
         <v>0.87</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>9.25</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45483</v>
+        <v>45484</v>
       </c>
       <c r="H62" t="n">
-        <v>2732</v>
+        <v>2698.05</v>
       </c>
       <c r="I62" t="n">
         <v>2708.817674489028</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K62" t="n">
-        <v>36.42</v>
+        <v>34.72</v>
       </c>
       <c r="L62" t="n">
         <v>1.97</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>4</v>
+      </c>
+      <c r="U62" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>10.57</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45554</v>
+        <v>45555</v>
       </c>
       <c r="H63" t="n">
-        <v>2797.5</v>
+        <v>2950.85</v>
       </c>
       <c r="I63" t="n">
         <v>2844.148491344751</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K63" t="n">
-        <v>-3.69</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="L63" t="n">
         <v>10.44</v>
@@ -4032,7 +4787,7 @@
         <v>2.45</v>
       </c>
       <c r="N63" t="n">
-        <v>3.47</v>
+        <v>5.48</v>
       </c>
       <c r="O63" t="n">
         <v>-1.24</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>9.539999999999999</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45586</v>
+        <v>45587</v>
       </c>
       <c r="H64" t="n">
-        <v>2998.2</v>
+        <v>2887.2</v>
       </c>
       <c r="I64" t="n">
         <v>2935.673143327235</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K64" t="n">
-        <v>1.6</v>
+        <v>-2.16</v>
       </c>
       <c r="L64" t="n">
         <v>5.16</v>
@@ -4089,7 +4856,7 @@
         <v>2.54</v>
       </c>
       <c r="N64" t="n">
-        <v>3.59</v>
+        <v>3.7</v>
       </c>
       <c r="O64" t="n">
         <v>5.48</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>11.93</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45617</v>
+        <v>45618</v>
       </c>
       <c r="H65" t="n">
-        <v>2936.25</v>
+        <v>3012.95</v>
       </c>
       <c r="I65" t="n">
         <v>3012.60050654419</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K65" t="n">
-        <v>-1.7</v>
+        <v>-4.36</v>
       </c>
       <c r="L65" t="n">
-        <v>4.24</v>
+        <v>6.11</v>
       </c>
       <c r="M65" t="n">
         <v>1.89</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>11.91</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45671</v>
+        <v>45672</v>
       </c>
       <c r="H66" t="n">
-        <v>3049.5</v>
+        <v>2960.25</v>
       </c>
       <c r="I66" t="n">
         <v>2974.530759663052</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K66" t="n">
-        <v>1.21</v>
+        <v>-1.75</v>
       </c>
       <c r="L66" t="n">
         <v>4.2</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>10.26</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45688</v>
+        <v>45689</v>
       </c>
       <c r="H67" t="n">
-        <v>2989.85</v>
+        <v>3076.75</v>
       </c>
       <c r="I67" t="n">
         <v>3048.794371051348</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K67" t="n">
-        <v>-1</v>
+        <v>-3.94</v>
       </c>
       <c r="L67" t="n">
-        <v>3.5</v>
+        <v>4.69</v>
       </c>
       <c r="M67" t="n">
         <v>0.95</v>
       </c>
       <c r="N67" t="n">
-        <v>2.12</v>
+        <v>2.91</v>
       </c>
       <c r="O67" t="n">
         <v>-2.93</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>9.869999999999999</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45702</v>
+        <v>45705</v>
       </c>
       <c r="H68" t="n">
-        <v>2942.6</v>
+        <v>2831.95</v>
       </c>
       <c r="I68" t="n">
         <v>2905.89568476119</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K68" t="n">
-        <v>-4.36</v>
+        <v>-7.96</v>
       </c>
       <c r="L68" t="n">
-        <v>5.52</v>
+        <v>9.25</v>
       </c>
       <c r="M68" t="n">
         <v>0.65</v>
       </c>
       <c r="N68" t="n">
-        <v>3.2</v>
+        <v>3.76</v>
       </c>
       <c r="O68" t="n">
         <v>2.91</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>12.75</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45764</v>
+        <v>45768</v>
       </c>
       <c r="H69" t="n">
-        <v>2679.4</v>
+        <v>2764</v>
       </c>
       <c r="I69" t="n">
         <v>2737.454916936956</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="K69" t="n">
-        <v>5.39</v>
+        <v>2.4</v>
       </c>
       <c r="L69" t="n">
         <v>4.35</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>10.86</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45897</v>
+        <v>45898</v>
       </c>
       <c r="H70" t="n">
-        <v>3295.3</v>
+        <v>3199.5</v>
       </c>
       <c r="I70" t="n">
         <v>3202.718673142857</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K70" t="n">
-        <v>19.22</v>
+        <v>15.76</v>
       </c>
       <c r="L70" t="n">
         <v>3.55</v>
@@ -4431,7 +5270,7 @@
         <v>2.89</v>
       </c>
       <c r="N70" t="n">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="O70" t="n">
         <v>3.16</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>6</v>
+      </c>
+      <c r="U70" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>8.16</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45903</v>
+        <v>45904</v>
       </c>
       <c r="H71" t="n">
-        <v>3286</v>
+        <v>3481.5</v>
       </c>
       <c r="I71" t="n">
         <v>3460.727387278857</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K71" t="n">
-        <v>-2.7</v>
+        <v>-8.81</v>
       </c>
       <c r="L71" t="n">
-        <v>4.08</v>
+        <v>10.95</v>
       </c>
       <c r="M71" t="n">
-        <v>1.07</v>
+        <v>7.33</v>
       </c>
       <c r="N71" t="n">
-        <v>3.62</v>
+        <v>5.95</v>
       </c>
       <c r="O71" t="n">
         <v>-2.91</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>7.89</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H72" t="n">
-        <v>3530</v>
+        <v>3396.5</v>
       </c>
       <c r="I72" t="n">
         <v>3404.018150352641</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K72" t="n">
-        <v>1.39</v>
+        <v>-2.44</v>
       </c>
       <c r="L72" t="n">
-        <v>0.52</v>
+        <v>2.58</v>
       </c>
       <c r="M72" t="n">
         <v>1.13</v>
       </c>
       <c r="N72" t="n">
-        <v>2.49</v>
+        <v>3.78</v>
       </c>
       <c r="O72" t="n">
         <v>5.95</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,22 +5456,22 @@
         <v>9.57</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="H73" t="n">
-        <v>3618.5</v>
+        <v>3690.2</v>
       </c>
       <c r="I73" t="n">
         <v>3659.871045102389</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K73" t="n">
-        <v>-6.54</v>
+        <v>-8.65</v>
       </c>
       <c r="L73" t="n">
-        <v>8.23</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M73" t="n">
         <v>1.22</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>3</v>
+      </c>
+      <c r="U73" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>7.59</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H74" t="n">
-        <v>3657.4</v>
+        <v>3557.5</v>
       </c>
       <c r="I74" t="n">
         <v>3629.785020023483</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.89</v>
+        <v>-3.6</v>
       </c>
       <c r="L74" t="n">
         <v>4.07</v>
@@ -4659,7 +5546,7 @@
         <v>1.29</v>
       </c>
       <c r="N74" t="n">
-        <v>1.95</v>
+        <v>2.73</v>
       </c>
       <c r="O74" t="n">
         <v>1.98</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>3</v>
+      </c>
+      <c r="U74" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -4695,22 +5594,22 @@
         <v>8.01</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="H75" t="n">
-        <v>3609.6</v>
+        <v>3675.8</v>
       </c>
       <c r="I75" t="n">
         <v>3674.752727841859</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K75" t="n">
-        <v>-1.46</v>
+        <v>-3.33</v>
       </c>
       <c r="L75" t="n">
-        <v>3.37</v>
+        <v>3.98</v>
       </c>
       <c r="M75" t="n">
         <v>5.05</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,22 +5663,22 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="H76" t="n">
-        <v>3431.8</v>
+        <v>3412.8</v>
       </c>
       <c r="I76" t="n">
         <v>3414.254967047823</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K76" t="n">
-        <v>-6.64</v>
+        <v>-7.15</v>
       </c>
       <c r="L76" t="n">
-        <v>6.92</v>
+        <v>7.44</v>
       </c>
       <c r="M76" t="n">
         <v>1.76</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>8.369999999999999</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="H77" t="n">
-        <v>3210.8</v>
+        <v>3300.8</v>
       </c>
       <c r="I77" t="n">
         <v>3295.256949869037</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K77" t="n">
-        <v>5.92</v>
+        <v>3.28</v>
       </c>
       <c r="L77" t="n">
         <v>2.76</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>4</v>
+      </c>
+      <c r="U77" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="78">
@@ -4866,22 +5801,22 @@
         <v>9.529999999999999</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="H78" t="n">
-        <v>3121.6</v>
+        <v>3045.6</v>
       </c>
       <c r="I78" t="n">
         <v>3060.143529036548</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K78" t="n">
-        <v>-5.43</v>
+        <v>-7.73</v>
       </c>
       <c r="L78" t="n">
-        <v>8.109999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="M78" t="n">
         <v>2.86</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,22 +5870,22 @@
         <v>9.529999999999999</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="H79" t="n">
-        <v>3136.9</v>
+        <v>3201.2</v>
       </c>
       <c r="I79" t="n">
         <v>3200.921583688909</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K79" t="n">
-        <v>-3</v>
+        <v>-5.11</v>
       </c>
       <c r="L79" t="n">
-        <v>5.35</v>
+        <v>5.49</v>
       </c>
       <c r="M79" t="n">
         <v>1.55</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4980,19 +5939,19 @@
         <v>8.56</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="H80" t="n">
-        <v>3282</v>
+        <v>3259</v>
       </c>
       <c r="I80" t="n">
         <v>3273.940122535194</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K80" t="n">
-        <v>2.52</v>
+        <v>1.81</v>
       </c>
       <c r="L80" t="n">
         <v>3.8</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>3</v>
+      </c>
+      <c r="U80" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -5061,6 +6032,14 @@
       <c r="Q81" t="n">
         <v>39</v>
       </c>
+      <c r="R81" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10019,7 +10998,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52.3</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="6">
@@ -10029,7 +11008,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -10039,7 +11018,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8">
@@ -10049,7 +11028,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -10059,7 +11038,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="10">
@@ -10069,7 +11048,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>98.8</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="11">
@@ -10079,7 +11058,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
@@ -10089,7 +11068,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
@@ -10099,7 +11078,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>39.2</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="14">
@@ -10109,7 +11088,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.34</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="15">
@@ -10119,7 +11098,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.01</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="16">
@@ -10129,7 +11108,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.61</v>
+        <v>-2.54</v>
       </c>
     </row>
     <row r="17">
@@ -10139,7 +11118,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>61.97</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="18">
@@ -10149,7 +11128,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48.1</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="19">
@@ -10159,7 +11138,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.27</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="20">
@@ -10169,7 +11148,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.35</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="21">
@@ -10179,7 +11158,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15.94</v>
+        <v>23.45</v>
       </c>
     </row>
     <row r="22">
@@ -10189,7 +11168,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
@@ -10199,7 +11178,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -10209,7 +11188,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="25">
@@ -10219,7 +11198,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.27</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="26">
@@ -10229,7 +11208,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.58</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="27">
@@ -10239,7 +11218,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>14.36</v>
+        <v>16.85</v>
       </c>
     </row>
     <row r="28">
@@ -10249,7 +11228,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29">
